--- a/Figure 4/Figure 4-B.xlsx
+++ b/Figure 4/Figure 4-B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983E1E5A-9B75-4316-8EED-5D653AB2A40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2534848-5420-4BF2-9CED-EC91AE00D5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31880" yWindow="2160" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -125,8 +125,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -149,11 +149,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -436,6 +437,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.6640625" style="2"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
